--- a/Unity/Assets/Config/Excel/DungeonSectionConfig.xlsx
+++ b/Unity/Assets/Config/Excel/DungeonSectionConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="21495" windowHeight="12045"/>
   </bookViews>
   <sheets>
     <sheet name="DungeonSectionProto" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="H3" authorId="0">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -70,11 +70,53 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
+  <si>
+    <t>##var</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>ChapterName</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>RandomArea</t>
+  </si>
+  <si>
+    <t>OpenLevel</t>
+  </si>
+  <si>
+    <t>ShenMiEnterID</t>
+  </si>
+  <si>
+    <t>Offset</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(array#sep=,),int</t>
+  </si>
+  <si>
+    <t>(array#sep=,),double</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>章节名称</t>
   </si>
   <si>
@@ -94,39 +136,6 @@
   </si>
   <si>
     <t>缩放</t>
-  </si>
-  <si>
-    <t>ChapterName</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>RandomArea</t>
-  </si>
-  <si>
-    <t>OpenLevel</t>
-  </si>
-  <si>
-    <t>ShenMiEnterID</t>
-  </si>
-  <si>
-    <t>Offset</t>
-  </si>
-  <si>
-    <t>Size</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int[]</t>
-  </si>
-  <si>
-    <t>double[]</t>
   </si>
   <si>
     <t>初章</t>
@@ -266,6 +275,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
@@ -275,13 +290,6 @@
     <font>
       <sz val="10"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -987,9 +995,9 @@
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -997,11 +1005,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1019,7 +1030,7 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
@@ -1118,8 +1129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="C4:F5" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C4:F5" etc:filterBottomFollowUsedRange="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="B1:E2" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:E2" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="4">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="ChapterName"/>
@@ -1417,249 +1428,261 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J20"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="7.5" customWidth="1"/>
-    <col min="4" max="5" width="16.75" customWidth="1"/>
-    <col min="6" max="8" width="33.625" customWidth="1"/>
-    <col min="9" max="9" width="24.875" customWidth="1"/>
+    <col min="2" max="2" width="7.5" customWidth="1"/>
+    <col min="3" max="4" width="16.75" customWidth="1"/>
+    <col min="5" max="7" width="33.625" customWidth="1"/>
+    <col min="8" max="8" width="24.875" customWidth="1"/>
+    <col min="9" max="9" width="20.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:10">
-      <c r="C3" s="3" t="s">
+    <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="12" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:10">
-      <c r="C4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="5" t="s">
+    <row r="2" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="B2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="D2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="F2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="11" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:10">
-      <c r="C5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>18</v>
+    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:9">
+      <c r="B4" s="7">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:10">
-      <c r="C6" s="6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>25</v>
+    <row r="5" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:9">
+      <c r="B5" s="9">
+        <v>2</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:10">
-      <c r="C7" s="8">
-        <v>2</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="7" t="s">
+    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:9">
+      <c r="B6" s="7">
+        <v>3</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:10">
-      <c r="C8" s="6">
-        <v>3</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>25</v>
+    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:9">
+      <c r="B7" s="9">
+        <v>4</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:10">
-      <c r="C9" s="8">
-        <v>4</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>43</v>
+    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:9">
+      <c r="B8" s="9">
+        <v>5</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:10">
-      <c r="C10" s="8">
-        <v>5</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="10" t="s">
+    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:9">
+      <c r="B9" s="9">
+        <v>6</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>43</v>
-      </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:10">
-      <c r="C11" s="8">
-        <v>6</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
+    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1"/>
+    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1"/>
     <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1"/>
     <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1"/>
     <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1"/>
@@ -1667,8 +1690,6 @@
     <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1"/>
     <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1"/>
     <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1"/>
-    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1"/>
-    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Unity/Assets/Config/Excel/DungeonSectionConfig.xlsx
+++ b/Unity/Assets/Config/Excel/DungeonSectionConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProjects\mengjing\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21495" windowHeight="12045"/>
+    <workbookView windowWidth="28800" windowHeight="12090"/>
   </bookViews>
   <sheets>
     <sheet name="DungeonSectionProto" sheetId="1" r:id="rId1"/>
@@ -138,7 +143,7 @@
     <t>缩放</t>
   </si>
   <si>
-    <t>初章</t>
+    <t>第一章</t>
   </si>
   <si>
     <t>洛兰森林</t>
@@ -231,7 +236,7 @@
     <t>-307,-79</t>
   </si>
   <si>
-    <t>终章</t>
+    <t>第六章</t>
   </si>
   <si>
     <t>沙漠圣地</t>
@@ -1015,6 +1020,9 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1029,9 +1037,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1463,7 +1468,7 @@
       <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1492,7 +1497,7 @@
       <c r="H2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1521,160 +1526,160 @@
       <c r="H3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:9">
-      <c r="B4" s="7">
+    <row r="4" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B4" s="8">
         <v>1</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>27</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:9">
-      <c r="B5" s="9">
+    <row r="5" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B5" s="10">
         <v>2</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="9" t="s">
         <v>33</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="2:9">
-      <c r="B6" s="7">
+    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B6" s="8">
         <v>3</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="9" t="s">
         <v>39</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:9">
-      <c r="B7" s="9">
+    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B7" s="10">
         <v>4</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="9" t="s">
         <v>45</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:9">
-      <c r="B8" s="9">
+    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B8" s="10">
         <v>5</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="2:9">
-      <c r="B9" s="9">
+    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:9">
+      <c r="B9" s="10">
         <v>6</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>58</v>
       </c>
       <c r="I9" s="1" t="s">
